--- a/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\nop-entropy\nop-runner\nop-cli\target\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\fliad-viid\fliad-plugin\fliad-plugin-hikvision\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDEA6E6-FE3E-49D6-A5EF-AD23DB84CB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AE940E-801D-4062-8CE0-65CCAF1DD42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
   <si>
     <t>序号</t>
   </si>
@@ -370,13 +370,41 @@
   <si>
     <t>IDX_HIKVISION_CAMERA_NAME</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fliad-plugin-hikvision</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad.hikvision.dao.entity</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad.hikvision</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1.0</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql,oracle,postgresql,h2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>fliad-hikvision</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -419,6 +447,13 @@
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1091,7 +1126,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1170,6 +1205,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1185,44 +1226,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1644,7 +1685,9 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9"/>
+      <c r="B2" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1653,7 +1696,9 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="27" t="s">
+        <v>117</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1662,7 +1707,9 @@
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="27" t="s">
+        <v>112</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1671,7 +1718,9 @@
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="27" t="s">
+        <v>113</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1680,7 +1729,9 @@
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="27" t="s">
+        <v>114</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1689,7 +1740,9 @@
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="27" t="s">
+        <v>111</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1698,7 +1751,9 @@
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="27" t="s">
+        <v>115</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1707,7 +1762,9 @@
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="27" t="s">
+        <v>115</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1716,7 +1773,9 @@
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="27" t="s">
+        <v>116</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
@@ -2008,55 +2067,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="26"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="28"/>
+      <c r="B1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
       <c r="F1" s="20" t="s">
         <v>34</v>
       </c>
       <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="F2" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="26"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="22" t="s">
         <v>0</v>
       </c>
@@ -2077,7 +2136,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="24"/>
@@ -2086,7 +2145,7 @@
       <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="24"/>
@@ -2095,7 +2154,7 @@
       <c r="G7" s="24"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="24"/>
@@ -2104,7 +2163,7 @@
       <c r="G8" s="24"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="24"/>
@@ -2113,7 +2172,7 @@
       <c r="G9" s="24"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
       <c r="D10" s="24"/>
@@ -2122,7 +2181,7 @@
       <c r="G10" s="24"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
       <c r="D11" s="24"/>
@@ -2131,7 +2190,7 @@
       <c r="G11" s="24"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
       <c r="D12" s="24"/>
@@ -2140,13 +2199,13 @@
       <c r="G12" s="24"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2190,146 +2249,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="I1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
       <c r="I2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
       <c r="I3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
       <c r="P3" s="14"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -2776,454 +2835,416 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+    </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="35" t="s">
+      <c r="A23" s="28"/>
+      <c r="B23" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="36" t="s">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="36"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="35" t="s">
+      <c r="A24" s="28"/>
+      <c r="B24" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="36" t="s">
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="N24" s="36"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-      <c r="Q24" s="37"/>
-      <c r="R24" s="37"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="35" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="36" t="s">
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="N25" s="36"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="35" t="s">
+      <c r="A26" s="28"/>
+      <c r="B26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
       <c r="H26" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="36" t="s">
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="N26" s="36"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="39" t="s">
+      <c r="A27" s="28"/>
+      <c r="B27" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
+      <c r="A28" s="28"/>
       <c r="B28" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
       <c r="G28" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="19"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="L28" s="36"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="40"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
+      <c r="A29" s="28"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
       <c r="J29" s="18"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
       <c r="J30" s="18"/>
       <c r="K30" s="3"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
+    </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="37"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31" t="s">
+      <c r="C34" s="35"/>
+      <c r="D34" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="31" t="s">
+      <c r="I34" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="35" t="s">
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>1</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43" t="s">
+      <c r="C35" s="33"/>
+      <c r="D35" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="43" t="s">
+      <c r="I35" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+    </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="37"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="37"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31" t="s">
+      <c r="C38" s="35"/>
+      <c r="D38" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
       <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="35" t="s">
+      <c r="I38" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35" t="s">
+      <c r="J38" s="36"/>
+      <c r="K38" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="35"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:R39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:R38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="M35:R35"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A33:R33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:R34"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="B27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:R5"/>
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A20:R20"/>
@@ -3240,17 +3261,51 @@
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:O4"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="B27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="A33:R33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M34:R34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="M35:R35"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:R38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:R39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\fliad-viid\fliad-plugin\fliad-plugin-hikvision\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AE940E-801D-4062-8CE0-65CCAF1DD42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01F1D91-229C-4BDD-A2A0-DC86E4658E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
   <si>
     <t>序号</t>
   </si>
@@ -393,10 +393,6 @@
   </si>
   <si>
     <t>mysql,oracle,postgresql,h2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>fliad-hikvision</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1226,44 +1222,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1697,7 +1693,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -2249,18 +2245,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="45" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
       <c r="I1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2277,18 +2273,18 @@
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="45" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="2" t="s">
         <v>35</v>
       </c>
@@ -2303,16 +2299,16 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="5" t="s">
         <v>42</v>
       </c>
@@ -2327,23 +2323,23 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -2369,26 +2365,26 @@
       <c r="R5" s="30"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -2855,33 +2851,33 @@
       <c r="R20" s="30"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="28"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
       <c r="F23" s="30"/>
@@ -2893,21 +2889,21 @@
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="28"/>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="36"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
@@ -2919,21 +2915,21 @@
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
       <c r="L24" s="30"/>
-      <c r="M24" s="41" t="s">
+      <c r="M24" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="N24" s="41"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="36"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="30"/>
       <c r="E25" s="30"/>
       <c r="F25" s="30"/>
@@ -2941,25 +2937,25 @@
       <c r="H25" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="41" t="s">
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="28"/>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="36"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="30"/>
       <c r="E26" s="30"/>
       <c r="F26" s="30"/>
@@ -2971,60 +2967,60 @@
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
       <c r="L26" s="30"/>
-      <c r="M26" s="41" t="s">
+      <c r="M26" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="N26" s="41"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="28"/>
       <c r="B28" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
       <c r="G28" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="41" t="s">
+      <c r="H28" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="41"/>
+      <c r="I28" s="38"/>
       <c r="J28" s="19"/>
-      <c r="K28" s="41" t="s">
+      <c r="K28" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="L28" s="41"/>
+      <c r="L28" s="38"/>
       <c r="M28" s="42"/>
       <c r="N28" s="42"/>
       <c r="O28" s="42"/>
@@ -3035,216 +3031,250 @@
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="28"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
       <c r="J29" s="18"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="28"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
       <c r="J30" s="18"/>
       <c r="K30" s="3"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
-      <c r="N33" s="37"/>
-      <c r="O33" s="37"/>
-      <c r="P33" s="37"/>
-      <c r="Q33" s="37"/>
-      <c r="R33" s="37"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="36"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35" t="s">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="35" t="s">
+      <c r="I34" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="36" t="s">
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>1</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33" t="s">
+      <c r="C35" s="45"/>
+      <c r="D35" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="37" t="s">
+      <c r="A37" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
-      <c r="R37" s="37"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35" t="s">
+      <c r="C38" s="33"/>
+      <c r="D38" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
       <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="36" t="s">
+      <c r="I38" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36" t="s">
+      <c r="J38" s="37"/>
+      <c r="K38" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="36"/>
-      <c r="P38" s="36"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="36"/>
+      <c r="L38" s="37"/>
+      <c r="M38" s="37"/>
+      <c r="N38" s="37"/>
+      <c r="O38" s="37"/>
+      <c r="P38" s="37"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
       <c r="L39" s="30"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:R39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:R38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="M35:R35"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A33:R33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M34:R34"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="B27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:R26"/>
     <mergeCell ref="A5:R5"/>
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A20:R20"/>
@@ -3261,51 +3291,17 @@
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="B27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="A33:R33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:R34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="M35:R35"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:R38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:R39"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="J2:O2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\fliad-viid\fliad-plugin\fliad-plugin-hikvision\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01F1D91-229C-4BDD-A2A0-DC86E4658E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EF8D08-86E7-4C05-B3DF-132412C8E4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="125">
   <si>
     <t>序号</t>
   </si>
@@ -140,260 +140,297 @@
     <t/>
   </si>
   <si>
+    <t>英文名</t>
+  </si>
+  <si>
+    <t>对象名</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>所属模块</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>字段列表</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>字段名</t>
+  </si>
+  <si>
+    <t>控件</t>
+  </si>
+  <si>
+    <t>显示</t>
+  </si>
+  <si>
+    <t>数据域</t>
+  </si>
+  <si>
+    <t>非空</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>字典</t>
+  </si>
+  <si>
+    <t>缺省值</t>
+  </si>
+  <si>
+    <t>扩展配置</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>CREATE_TIME</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>UPDATE_TIME</t>
+  </si>
+  <si>
+    <t>关联列表</t>
+  </si>
+  <si>
+    <t>属性名</t>
+  </si>
+  <si>
+    <t>关联属性名</t>
+  </si>
+  <si>
+    <t>关联对象</t>
+  </si>
+  <si>
+    <t>关联类型</t>
+  </si>
+  <si>
+    <t>关联中文名</t>
+  </si>
+  <si>
+    <t>关联英文名</t>
+  </si>
+  <si>
+    <t>忽略依赖</t>
+  </si>
+  <si>
+    <t>排序条件</t>
+  </si>
+  <si>
+    <t>关联条件</t>
+  </si>
+  <si>
+    <t>左属性</t>
+  </si>
+  <si>
+    <t>左值</t>
+  </si>
+  <si>
+    <t>右属性</t>
+  </si>
+  <si>
+    <t>右值</t>
+  </si>
+  <si>
+    <t>唯一键列表</t>
+  </si>
+  <si>
+    <t>唯一键名</t>
+  </si>
+  <si>
+    <t>数据库约束名</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>别名列表</t>
+  </si>
+  <si>
+    <t>属性路径</t>
+  </si>
+  <si>
+    <t>INTEGER</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>密码</t>
+  </si>
+  <si>
+    <t>hikvision_camera</t>
+  </si>
+  <si>
+    <t>HikvisionCamera</t>
+  </si>
+  <si>
+    <t>海康布防表</t>
+  </si>
+  <si>
+    <t>DEVICE_ID</t>
+  </si>
+  <si>
+    <t>设备编号</t>
+  </si>
+  <si>
+    <t>设备名称</t>
+  </si>
+  <si>
+    <t>IP_ADDR</t>
+  </si>
+  <si>
+    <t>设备IP地址</t>
+  </si>
+  <si>
+    <t>PORT</t>
+  </si>
+  <si>
+    <t>端口号</t>
+  </si>
+  <si>
+    <t>USERNAME</t>
+  </si>
+  <si>
+    <t>用户名</t>
+  </si>
+  <si>
+    <t>ENABLE_STATUS</t>
+  </si>
+  <si>
+    <t>启用状态：1=启用，0=禁用</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ONLINE_STATUS</t>
+  </si>
+  <si>
+    <t>在线状态：1=在线，0=离线</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>IDX_HIKVISION_CAMERA_NAME</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>IDX_HIKVISION_CAMERA_NAME</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fliad-plugin-hikvision</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad.hikvision.dao.entity</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad.hikvision</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.fliad</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1.0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql,oracle,postgresql,h2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>值类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>英文名</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>描述</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>字典项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>代码</t>
-  </si>
-  <si>
-    <t>对象名</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>所属模块</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>字段列表</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>控件</t>
-  </si>
-  <si>
-    <t>显示</t>
-  </si>
-  <si>
-    <t>数据域</t>
-  </si>
-  <si>
-    <t>非空</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>字典</t>
-  </si>
-  <si>
-    <t>缺省值</t>
-  </si>
-  <si>
-    <t>扩展配置</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>VARCHAR</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>CREATE_TIME</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
-    <t>DATETIME</t>
-  </si>
-  <si>
-    <t>UPDATE_TIME</t>
-  </si>
-  <si>
-    <t>关联列表</t>
-  </si>
-  <si>
-    <t>属性名</t>
-  </si>
-  <si>
-    <t>关联属性名</t>
-  </si>
-  <si>
-    <t>关联对象</t>
-  </si>
-  <si>
-    <t>关联类型</t>
-  </si>
-  <si>
-    <t>关联中文名</t>
-  </si>
-  <si>
-    <t>关联英文名</t>
-  </si>
-  <si>
-    <t>忽略依赖</t>
-  </si>
-  <si>
-    <t>排序条件</t>
-  </si>
-  <si>
-    <t>关联条件</t>
-  </si>
-  <si>
-    <t>左属性</t>
-  </si>
-  <si>
-    <t>左值</t>
-  </si>
-  <si>
-    <t>右属性</t>
-  </si>
-  <si>
-    <t>右值</t>
-  </si>
-  <si>
-    <t>唯一键列表</t>
-  </si>
-  <si>
-    <t>唯一键名</t>
-  </si>
-  <si>
-    <t>数据库约束名</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>别名列表</t>
-  </si>
-  <si>
-    <t>属性路径</t>
-  </si>
-  <si>
-    <t>INTEGER</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>密码</t>
-  </si>
-  <si>
-    <t>hikvision_camera</t>
-  </si>
-  <si>
-    <t>HikvisionCamera</t>
-  </si>
-  <si>
-    <t>海康布防表</t>
-  </si>
-  <si>
-    <t>DEVICE_ID</t>
-  </si>
-  <si>
-    <t>设备编号</t>
-  </si>
-  <si>
-    <t>设备名称</t>
-  </si>
-  <si>
-    <t>IP_ADDR</t>
-  </si>
-  <si>
-    <t>设备IP地址</t>
-  </si>
-  <si>
-    <t>PORT</t>
-  </si>
-  <si>
-    <t>端口号</t>
-  </si>
-  <si>
-    <t>USERNAME</t>
-  </si>
-  <si>
-    <t>用户名</t>
-  </si>
-  <si>
-    <t>ENABLE_STATUS</t>
-  </si>
-  <si>
-    <t>启用状态：1=启用，0=禁用</t>
-  </si>
-  <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>ONLINE_STATUS</t>
-  </si>
-  <si>
-    <t>在线状态：1=在线，0=离线</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>IDX_HIKVISION_CAMERA_NAME</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>IDX_HIKVISION_CAMERA_NAME</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁用</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>fliad-plugin-hikvision</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>com.fliad.hikvision.dao.entity</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>com.fliad.hikvision</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>com.fliad</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1.0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>mysql,oracle,postgresql,h2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>hikvision/enableStatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用状态</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -414,14 +451,6 @@
       <color rgb="FF0563C1"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -450,6 +479,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="10">
@@ -497,18 +533,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EEDA"/>
+        <fgColor rgb="FFFFF2CB"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CB"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -734,9 +770,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -757,36 +791,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -826,7 +834,7 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -846,6 +854,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -871,7 +892,7 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -906,19 +927,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1045,12 +1053,8 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1060,54 +1064,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1118,11 +1075,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1174,92 +1131,125 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1651,7 +1641,7 @@
       <c r="D9" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1681,7 +1671,7 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="26" t="b">
+      <c r="B2" s="22" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1692,8 +1682,8 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>111</v>
+      <c r="B3" s="23" t="s">
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -1703,8 +1693,8 @@
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>112</v>
+      <c r="B4" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1714,8 +1704,8 @@
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>113</v>
+      <c r="B5" s="23" t="s">
+        <v>108</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
@@ -1725,8 +1715,8 @@
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>114</v>
+      <c r="B6" s="23" t="s">
+        <v>109</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
@@ -1736,8 +1726,8 @@
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>111</v>
+      <c r="B7" s="23" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -1747,8 +1737,8 @@
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>115</v>
+      <c r="B8" s="23" t="s">
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -1758,8 +1748,8 @@
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>115</v>
+      <c r="B9" s="23" t="s">
+        <v>110</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
@@ -1769,8 +1759,8 @@
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>116</v>
+      <c r="B10" s="23" t="s">
+        <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
@@ -1813,7 +1803,7 @@
       <c r="C16" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2048,174 +2038,152 @@
       <c r="G19" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B8FF45-D262-49D2-AC61-A5C2FBF58806}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.08203125" customWidth="1"/>
-    <col min="2" max="7" width="8.5" customWidth="1"/>
+    <col min="2" max="4" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="19.08203125" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="17.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="17"/>
+      <c r="A1" s="32">
+        <v>1</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="41"/>
+      <c r="F1" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="25"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="33"/>
+      <c r="B3" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="41"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="33"/>
+      <c r="B5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="33"/>
+      <c r="B6" s="25">
+        <v>1</v>
+      </c>
+      <c r="C6" s="25">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33"/>
+      <c r="B7" s="25">
         <v>2</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="22" t="s">
+      <c r="C7" s="27">
         <v>0</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="D7" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="28"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:A13"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B13:G13"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2245,183 +2213,183 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
       <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+        <v>35</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
       <c r="I2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
+        <v>34</v>
+      </c>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="A3" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
+        <v>37</v>
+      </c>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
       <c r="P3" s="14"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
+      <c r="A4" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
+      <c r="A6" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>30</v>
@@ -2430,16 +2398,16 @@
         <v>31</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -2447,25 +2415,25 @@
         <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="7"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M8" s="7">
         <v>20</v>
@@ -2485,13 +2453,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="7"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -2499,7 +2467,7 @@
         <v>33</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M9" s="7">
         <v>64</v>
@@ -2519,21 +2487,21 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="7"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M10" s="7">
         <v>128</v>
@@ -2553,21 +2521,21 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="7"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M11" s="7">
         <v>64</v>
@@ -2587,21 +2555,21 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="7"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -2619,21 +2587,21 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="7"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M13" s="7">
         <v>64</v>
@@ -2653,21 +2621,21 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="7"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M14" s="7">
         <v>128</v>
@@ -2687,27 +2655,27 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="7"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="1"/>
@@ -2721,27 +2689,27 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="7"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="1"/>
@@ -2755,21 +2723,21 @@
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="7"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -2787,21 +2755,21 @@
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="7"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -2831,450 +2799,416 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="55"/>
+      <c r="B23" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="52"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="55"/>
+      <c r="B24" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" s="52"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="55"/>
+      <c r="B25" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="37" t="s">
+      <c r="C25" s="47"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="2" t="s">
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="38" t="s">
+      <c r="N25" s="52"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45"/>
+      <c r="R25" s="45"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="55"/>
+      <c r="B26" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="38"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="38" t="s">
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" s="52"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="55"/>
+      <c r="B27" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="N24" s="38"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="N25" s="38"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="N26" s="38"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
+      <c r="A28" s="55"/>
       <c r="B28" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
+      <c r="C28" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
       <c r="G28" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="38"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
+        <v>71</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="52"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="L28" s="52"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
+      <c r="A29" s="55"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="18"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="17"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="18"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="17"/>
       <c r="K30" s="3"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
+      <c r="A33" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="48"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
+      <c r="B34" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
       <c r="G34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-      <c r="R34" s="37"/>
+        <v>34</v>
+      </c>
+      <c r="I34" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>1</v>
       </c>
-      <c r="B35" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
+      <c r="B35" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="39"/>
+      <c r="I35" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="45"/>
+      <c r="P35" s="45"/>
+      <c r="Q35" s="45"/>
+      <c r="R35" s="45"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="36"/>
-      <c r="Q37" s="36"/>
-      <c r="R37" s="36"/>
+      <c r="A37" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="48"/>
+      <c r="R37" s="48"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
       <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I38" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="37"/>
-      <c r="K38" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="L38" s="37"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-      <c r="Q38" s="37"/>
-      <c r="R38" s="37"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="47"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="47"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="39"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="45"/>
+      <c r="Q39" s="45"/>
+      <c r="R39" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:R39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:R38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="M35:R35"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A33:R33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:R34"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="B27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:R5"/>
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A20:R20"/>
@@ -3291,19 +3225,53 @@
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:O4"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="B27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="A33:R33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M34:R34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="M35:R35"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:R38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:R39"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/fliad-plugin-hikvision/model/hikvision.orm.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\fliad-viid\fliad-plugin\fliad-plugin-hikvision\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EF8D08-86E7-4C05-B3DF-132412C8E4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548D85A3-B338-4B45-9CD6-48A43064553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
     <sheet name="配置" sheetId="2" r:id="rId2"/>
     <sheet name="域定义" sheetId="3" r:id="rId3"/>
     <sheet name="字典定义" sheetId="4" r:id="rId4"/>
-    <sheet name="hikvision_camera" sheetId="22" r:id="rId5"/>
+    <sheet name="HIKVISION_CAMERA" sheetId="22" r:id="rId5"/>
+    <sheet name="VEHICLE_TRAFFIC_RECORD" sheetId="23" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="191">
   <si>
     <t>序号</t>
   </si>
@@ -288,9 +289,6 @@
   </si>
   <si>
     <t>密码</t>
-  </si>
-  <si>
-    <t>hikvision_camera</t>
   </si>
   <si>
     <t>HikvisionCamera</t>
@@ -430,6 +428,209 @@
   </si>
   <si>
     <t>启用状态</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>VehicleTrafficRecord</t>
+  </si>
+  <si>
+    <t>车辆通行记录信息表</t>
+  </si>
+  <si>
+    <t>KKBH</t>
+  </si>
+  <si>
+    <t>卡口编号，符合GA/T 16.31与GA/T 543.10要求</t>
+  </si>
+  <si>
+    <t>FXLX</t>
+  </si>
+  <si>
+    <t>方向类型</t>
+  </si>
+  <si>
+    <t>CDH</t>
+  </si>
+  <si>
+    <t>车道号</t>
+  </si>
+  <si>
+    <t>GCSJ</t>
+  </si>
+  <si>
+    <t>过车时间，格式yyyy-mm-dd hh24:mi:ss</t>
+  </si>
+  <si>
+    <t>WFDM</t>
+  </si>
+  <si>
+    <t>违法行为，符合GA/T 16.31与GA/T 543.5要求</t>
+  </si>
+  <si>
+    <t>HPHM</t>
+  </si>
+  <si>
+    <t>号牌号码，符合GA/T 543.5要求，无牌等用"-"表示</t>
+  </si>
+  <si>
+    <t>HPZL</t>
+  </si>
+  <si>
+    <t>号牌种类，符合GA/T 16.7与GA/T 543.5要求：01-大型汽车,02-小型汽车,...,99-其他号牌</t>
+  </si>
+  <si>
+    <t>HPYS</t>
+  </si>
+  <si>
+    <t>号牌颜色，符合GB 1.1-2009：0-白色,1-黄色,2-蓝色,3-黑色,4-绿色,5-未识别,9-其他颜色</t>
+  </si>
+  <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>FZHPHM</t>
+  </si>
+  <si>
+    <t>辅助号牌号码，无牌等用"-"表示</t>
+  </si>
+  <si>
+    <t>FZHPZL</t>
+  </si>
+  <si>
+    <t>辅助号牌种类，符合GA/T 16.7与GA/T 543.5要求</t>
+  </si>
+  <si>
+    <t>FZHPYS</t>
+  </si>
+  <si>
+    <t>辅助号牌颜色：0-白色,1-黄色,2-蓝色,3-黑色,4-绿色,5-未识别,9-其他颜色</t>
+  </si>
+  <si>
+    <t>CLLX</t>
+  </si>
+  <si>
+    <t>车辆类型，符合GA/T 16.4与GA/T 543.5要求</t>
+  </si>
+  <si>
+    <t>CWKC</t>
+  </si>
+  <si>
+    <t>车外廓长，单位厘米，最长5位</t>
+  </si>
+  <si>
+    <t>CLPP</t>
+  </si>
+  <si>
+    <t>车辆品牌，符合GA/T 543.10要求</t>
+  </si>
+  <si>
+    <t>CSYS</t>
+  </si>
+  <si>
+    <t>车身颜色，符合GA/T 16.8与GA/T 543.5：A-白,B-灰,C-黄,D-粉,E-红,F-紫,G-绿,H-蓝,I-棕,J-黑</t>
+  </si>
+  <si>
+    <t>HPKXD</t>
+  </si>
+  <si>
+    <t>号牌识别可信度，0~100%</t>
+  </si>
+  <si>
+    <t>MWHPKXD</t>
+  </si>
+  <si>
+    <t>每位号牌识别可信度，格式如"苏-80,B-90,..."</t>
+  </si>
+  <si>
+    <t>CXKXD</t>
+  </si>
+  <si>
+    <t>车型识别可信度，0~100%</t>
+  </si>
+  <si>
+    <t>PPKXD</t>
+  </si>
+  <si>
+    <t>品牌识别可信度，0~100%</t>
+  </si>
+  <si>
+    <t>XWTZ</t>
+  </si>
+  <si>
+    <t>行为特征，1-不系安全带;2-拨打电话;...多个用分号分隔</t>
+  </si>
+  <si>
+    <t>TPLJ</t>
+  </si>
+  <si>
+    <t>图片路径</t>
+  </si>
+  <si>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>通行图片1</t>
+  </si>
+  <si>
+    <t>TP2</t>
+  </si>
+  <si>
+    <t>通行图片2</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
+    <t>通行图片3</t>
+  </si>
+  <si>
+    <t>TZTP</t>
+  </si>
+  <si>
+    <t>特征图片</t>
+  </si>
+  <si>
+    <t>JSRTP</t>
+  </si>
+  <si>
+    <t>驾驶人图片</t>
+  </si>
+  <si>
+    <t>CLSD</t>
+  </si>
+  <si>
+    <t>车辆速度，单位km/h</t>
+  </si>
+  <si>
+    <t>TID</t>
+  </si>
+  <si>
+    <t>rfid标签芯片识别号</t>
+  </si>
+  <si>
+    <t>ZKRS</t>
+  </si>
+  <si>
+    <t>载客人数</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>rfid标识卡号码</t>
+  </si>
+  <si>
+    <t>SXJBH</t>
+  </si>
+  <si>
+    <t>摄像机设备编号</t>
+  </si>
+  <si>
+    <t>HIKVISION_CAMERA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>VEHICLE_TRAFFIC_RECORD</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1079,7 +1280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1167,6 +1368,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1250,6 +1484,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1683,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -1694,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1705,7 +1966,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
@@ -1716,7 +1977,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
@@ -1727,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -1738,7 +1999,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -1749,7 +2010,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
@@ -1760,7 +2021,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
@@ -2056,84 +2317,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="32">
+      <c r="A1" s="43">
         <v>1</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="50"/>
+      <c r="D1" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="52"/>
+      <c r="F1" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40" t="s">
+      <c r="G1" s="24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="44"/>
+      <c r="B2" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="33"/>
-      <c r="B2" s="38" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="25"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="44"/>
+      <c r="B3" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="38" t="s">
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="52"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="44"/>
+      <c r="B4" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="41"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>120</v>
-      </c>
       <c r="F5" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="25">
         <v>1</v>
       </c>
@@ -2141,14 +2402,14 @@
         <v>1</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="25">
         <v>2</v>
       </c>
@@ -2156,20 +2417,20 @@
         <v>0</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="28"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2196,7 +2457,7 @@
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="4.4140625" customWidth="1"/>
     <col min="3" max="3" width="16.9140625" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="4.6640625" customWidth="1"/>
     <col min="6" max="6" width="4.75" customWidth="1"/>
     <col min="7" max="7" width="15.08203125" customWidth="1"/>
@@ -2207,152 +2468,152 @@
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="6.08203125" customWidth="1"/>
     <col min="14" max="14" width="8.25" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="19.9140625" customWidth="1"/>
     <col min="16" max="16" width="11.08203125" customWidth="1"/>
     <col min="17" max="18" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
+      <c r="J1" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
       <c r="I2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
       <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
       <c r="P3" s="14"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -2453,13 +2714,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="7"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -2493,7 +2754,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -2521,13 +2782,13 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="7"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -2555,13 +2816,13 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="7"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -2587,13 +2848,13 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="7"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -2655,13 +2916,13 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="7"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -2669,13 +2930,15 @@
         <v>53</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="9"/>
+      <c r="O15" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="P15" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="1"/>
@@ -2689,13 +2952,13 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="7"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -2703,13 +2966,13 @@
         <v>53</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="1"/>
@@ -2799,402 +3062,402 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="55"/>
+      <c r="P20" s="55"/>
+      <c r="Q20" s="55"/>
+      <c r="R20" s="55"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="55"/>
-      <c r="B23" s="47" t="s">
+      <c r="A23" s="66"/>
+      <c r="B23" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
       <c r="H23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="52" t="s">
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="N23" s="52"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="56"/>
+      <c r="R23" s="56"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="66"/>
+      <c r="B24" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
       <c r="H24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="52" t="s">
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="N24" s="52"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="56"/>
+      <c r="R24" s="56"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="55"/>
-      <c r="B25" s="47" t="s">
+      <c r="A25" s="66"/>
+      <c r="B25" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
       <c r="H25" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="52" t="s">
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="N25" s="52"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="56"/>
+      <c r="R25" s="56"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="55"/>
-      <c r="B26" s="47" t="s">
+      <c r="A26" s="66"/>
+      <c r="B26" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
       <c r="H26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="52" t="s">
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="N26" s="52"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="56"/>
+      <c r="R26" s="56"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
-      <c r="B27" s="51" t="s">
+      <c r="A27" s="66"/>
+      <c r="B27" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="55"/>
+      <c r="A28" s="66"/>
       <c r="B28" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
       <c r="G28" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="52" t="s">
+      <c r="H28" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="I28" s="52"/>
+      <c r="I28" s="63"/>
       <c r="J28" s="18"/>
-      <c r="K28" s="52" t="s">
+      <c r="K28" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="55"/>
+      <c r="A29" s="66"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
       <c r="J29" s="17"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="55"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
       <c r="J30" s="17"/>
       <c r="K30" s="3"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="59"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="59"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="59"/>
+      <c r="P33" s="59"/>
+      <c r="Q33" s="59"/>
+      <c r="R33" s="59"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46" t="s">
+      <c r="C34" s="57"/>
+      <c r="D34" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
       <c r="G34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="46" t="s">
+      <c r="I34" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="47" t="s">
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="58"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>1</v>
       </c>
-      <c r="B35" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43" t="s">
+      <c r="B35" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45"/>
+      <c r="I35" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="56"/>
+      <c r="R35" s="56"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="48"/>
-      <c r="R37" s="48"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
+      <c r="R37" s="59"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46" t="s">
+      <c r="C38" s="57"/>
+      <c r="D38" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
       <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I38" s="47" t="s">
+      <c r="I38" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47" t="s">
+      <c r="J38" s="58"/>
+      <c r="K38" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="45"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="72">
@@ -3274,4 +3537,1772 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7DA6D2-1B65-439E-85BB-2A7C98FA0C7C}">
+  <dimension ref="A1:R60"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="42.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="25">
+        <v>20</v>
+      </c>
+      <c r="N8" s="25"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="26"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
+        <v>2</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="25">
+        <v>50</v>
+      </c>
+      <c r="N9" s="25"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="26"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="25">
+        <v>3</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="25">
+        <v>20</v>
+      </c>
+      <c r="N10" s="25"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="26"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="25">
+        <v>4</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="25">
+        <v>10</v>
+      </c>
+      <c r="N11" s="25"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="26"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="25">
+        <v>5</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="26"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="25">
+        <v>6</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="25">
+        <v>20</v>
+      </c>
+      <c r="N13" s="25"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="26"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="25">
+        <v>7</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="25">
+        <v>20</v>
+      </c>
+      <c r="N14" s="25"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="26"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="25">
+        <v>8</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="25">
+        <v>2</v>
+      </c>
+      <c r="N15" s="25"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="26"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="25">
+        <v>9</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="28"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="26"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="25">
+        <v>10</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="25">
+        <v>20</v>
+      </c>
+      <c r="N17" s="25"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="26"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="25">
+        <v>11</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="25">
+        <v>2</v>
+      </c>
+      <c r="N18" s="25"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="26"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="25">
+        <v>12</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="26"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
+        <v>13</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="25">
+        <v>20</v>
+      </c>
+      <c r="N20" s="25"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="26"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
+        <v>14</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="25">
+        <v>5</v>
+      </c>
+      <c r="N21" s="25"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="26"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
+        <v>15</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="25">
+        <v>50</v>
+      </c>
+      <c r="N22" s="25"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="26"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="25">
+        <v>16</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="25">
+        <v>2</v>
+      </c>
+      <c r="N23" s="25"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="26"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="25">
+        <v>17</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="26"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="25">
+        <v>18</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="28"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="25">
+        <v>200</v>
+      </c>
+      <c r="N25" s="25"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="26"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="25">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="26"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
+        <v>20</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" s="28"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="26"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
+        <v>21</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="25">
+        <v>50</v>
+      </c>
+      <c r="N28" s="25"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="26"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="25">
+        <v>22</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="25">
+        <v>255</v>
+      </c>
+      <c r="N29" s="25"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="26"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="25">
+        <v>23</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="25">
+        <v>255</v>
+      </c>
+      <c r="N30" s="25"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="26"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="25">
+        <v>24</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="25">
+        <v>255</v>
+      </c>
+      <c r="N31" s="25"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="26"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="25">
+        <v>25</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="28"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="25">
+        <v>255</v>
+      </c>
+      <c r="N32" s="25"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="26"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <v>26</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="25">
+        <v>255</v>
+      </c>
+      <c r="N33" s="25"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="26"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="25">
+        <v>27</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="25">
+        <v>255</v>
+      </c>
+      <c r="N34" s="25"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="26"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
+        <v>28</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="28"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="26"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <v>29</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" s="28"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="25">
+        <v>50</v>
+      </c>
+      <c r="N36" s="25"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="26"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <v>30</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="28"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L37" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="26"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="25">
+        <v>31</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="28"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="25">
+        <v>50</v>
+      </c>
+      <c r="N38" s="25"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="26"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
+        <v>32</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L39" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="25">
+        <v>50</v>
+      </c>
+      <c r="N39" s="25"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="26"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="25"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="26"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="68"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="68"/>
+      <c r="Q41" s="68"/>
+      <c r="R41" s="68"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="70"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="70"/>
+      <c r="N43" s="70"/>
+      <c r="O43" s="70"/>
+      <c r="P43" s="70"/>
+      <c r="Q43" s="70"/>
+      <c r="R43" s="70"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" s="66"/>
+      <c r="B44" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="68"/>
+      <c r="H44" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" s="68"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" s="74"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="69"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="69"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="66"/>
+      <c r="B45" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" s="74"/>
+      <c r="O45" s="69"/>
+      <c r="P45" s="69"/>
+      <c r="Q45" s="69"/>
+      <c r="R45" s="69"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" s="66"/>
+      <c r="B46" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
+      <c r="L46" s="48"/>
+      <c r="M46" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="N46" s="74"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="69"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" s="66"/>
+      <c r="B47" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="71"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="N47" s="74"/>
+      <c r="O47" s="69"/>
+      <c r="P47" s="69"/>
+      <c r="Q47" s="69"/>
+      <c r="R47" s="69"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" s="66"/>
+      <c r="B48" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="76"/>
+      <c r="N48" s="76"/>
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="76"/>
+      <c r="R48" s="76"/>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" s="66"/>
+      <c r="B49" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="H49" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="I49" s="74"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="74" t="s">
+        <v>73</v>
+      </c>
+      <c r="L49" s="74"/>
+      <c r="M49" s="75"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="75"/>
+      <c r="P49" s="75"/>
+      <c r="Q49" s="75"/>
+      <c r="R49" s="75"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" s="66"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="72"/>
+      <c r="I50" s="72"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="73"/>
+      <c r="O50" s="73"/>
+      <c r="P50" s="73"/>
+      <c r="Q50" s="73"/>
+      <c r="R50" s="73"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" s="66"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="72"/>
+      <c r="F51" s="72"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="72"/>
+      <c r="I51" s="72"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="39"/>
+      <c r="M51" s="73"/>
+      <c r="N51" s="73"/>
+      <c r="O51" s="73"/>
+      <c r="P51" s="73"/>
+      <c r="Q51" s="73"/>
+      <c r="R51" s="73"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
+      <c r="M54" s="70"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="70"/>
+      <c r="Q54" s="70"/>
+      <c r="R54" s="70"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="J55" s="71"/>
+      <c r="K55" s="71"/>
+      <c r="L55" s="71"/>
+      <c r="M55" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="N55" s="71"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="71"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56" s="25"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="68"/>
+      <c r="J56" s="68"/>
+      <c r="K56" s="68"/>
+      <c r="L56" s="68"/>
+      <c r="M56" s="69"/>
+      <c r="N56" s="69"/>
+      <c r="O56" s="69"/>
+      <c r="P56" s="69"/>
+      <c r="Q56" s="69"/>
+      <c r="R56" s="69"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="70"/>
+      <c r="I58" s="70"/>
+      <c r="J58" s="70"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="70"/>
+      <c r="M58" s="70"/>
+      <c r="N58" s="70"/>
+      <c r="O58" s="70"/>
+      <c r="P58" s="70"/>
+      <c r="Q58" s="70"/>
+      <c r="R58" s="70"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="71"/>
+      <c r="D59" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="71"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I59" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" s="71"/>
+      <c r="K59" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="71"/>
+      <c r="M59" s="71"/>
+      <c r="N59" s="71"/>
+      <c r="O59" s="71"/>
+      <c r="P59" s="71"/>
+      <c r="Q59" s="71"/>
+      <c r="R59" s="71"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" s="25"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="68"/>
+      <c r="D60" s="68"/>
+      <c r="E60" s="68"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="68"/>
+      <c r="J60" s="68"/>
+      <c r="K60" s="68"/>
+      <c r="L60" s="68"/>
+      <c r="M60" s="69"/>
+      <c r="N60" s="69"/>
+      <c r="O60" s="69"/>
+      <c r="P60" s="69"/>
+      <c r="Q60" s="69"/>
+      <c r="R60" s="69"/>
+    </row>
+  </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="A43:R43"/>
+    <mergeCell ref="A44:A51"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="O44:R44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="O48:R48"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="O45:R45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="O46:R46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:R47"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="M55:R55"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="O49:R49"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="O50:R50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="O51:R51"/>
+    <mergeCell ref="A54:R54"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="M59:R59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="M56:R56"/>
+    <mergeCell ref="A58:R58"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:R60"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>